--- a/docs/downloads/04/tbl_homeland_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_feramanga_atsimo.xlsx
@@ -397,12 +397,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>40</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -420,12 +414,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -443,12 +431,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,12 +448,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -511,12 +487,6 @@
         <is>
           <t>3</t>
         </is>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
       </c>
     </row>
     <row r="8">
